--- a/artfynd/A 40537-2021 artfynd.xlsx
+++ b/artfynd/A 40537-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40537-2021 artfynd.xlsx
+++ b/artfynd/A 40537-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>72748048</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 40537-2021 artfynd.xlsx
+++ b/artfynd/A 40537-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72748048</v>
+        <v>92684046</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,53 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SÖ St. Dammsjön, Dlr</t>
+          <t>Stora Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520914</v>
+        <v>521015</v>
       </c>
       <c r="R2" t="n">
-        <v>6677272</v>
+        <v>6677763</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-08-18</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-08-18</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,61 +757,56 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Olsson</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Olsson</t>
+          <t>Stig-Åke Svenson, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92684101</v>
+        <v>92684075</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520868.9146750448</v>
+        <v>520975</v>
       </c>
       <c r="R3" t="n">
-        <v>6677385.8885972</v>
+        <v>6677734</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,19 +847,9 @@
           <t>2021-04-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-04-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +870,225 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>72748048</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SÖ St. Dammsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>520914</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6677272</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-08-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-08-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Håkan Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>92684101</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stora Dammsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>520869</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6677386</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40537-2021 artfynd.xlsx
+++ b/artfynd/A 40537-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92684046</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92684075</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72748048</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,8 +1109,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92684101</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>